--- a/Backend/CenterBackend/Report/日报表/2026-03/日报表-2026-03-13.xlsx
+++ b/Backend/CenterBackend/Report/日报表/2026-03/日报表-2026-03-13.xlsx
@@ -42424,35 +42424,61 @@
       <c r="C7" s="246"/>
       <c r="D7" s="272">
         <f>J7+U7</f>
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="E7" s="271">
         <f>K7+V7</f>
-        <v>0</v>
+        <v>83.09999084472656</v>
       </c>
       <c r="F7" s="271"/>
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="321"/>
-      <c r="J7" s="320"/>
-      <c r="K7" s="319"/>
-      <c r="L7" s="319"/>
+      <c r="G7" s="271">
+        <v>0</v>
+      </c>
+      <c r="H7" s="271">
+        <v>0</v>
+      </c>
+      <c r="I7" s="321">
+        <v>0</v>
+      </c>
+      <c r="J7" s="320">
+        <v>0</v>
+      </c>
+      <c r="K7" s="319">
+        <v>0</v>
+      </c>
+      <c r="L7" s="319">
+        <v>0</v>
+      </c>
       <c r="M7" s="319"/>
       <c r="N7" s="319"/>
-      <c r="O7" s="319"/>
+      <c r="O7" s="319">
+        <v>0</v>
+      </c>
       <c r="P7" s="319"/>
       <c r="Q7" s="319"/>
-      <c r="R7" s="319"/>
+      <c r="R7" s="319">
+        <v>0</v>
+      </c>
       <c r="S7" s="318"/>
       <c r="T7" s="317"/>
-      <c r="U7" s="316"/>
-      <c r="V7" s="315"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="271"/>
-      <c r="Y7" s="271"/>
-      <c r="Z7" s="314" t="e">
+      <c r="U7" s="316">
+        <v>0</v>
+      </c>
+      <c r="V7" s="315">
+        <v>0</v>
+      </c>
+      <c r="W7" s="267">
+        <v>0</v>
+      </c>
+      <c r="X7" s="271">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="271">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="314">
         <f>U7/D7</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="313"/>
       <c r="AB7" s="300"/>
@@ -42468,8 +42494,8 @@
     <row r="8" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="247"/>
       <c r="C8" s="246"/>
-      <c r="D8" s="292">
-        <v>51</v>
+      <c r="D8" s="292" t="s">
+        <v>378</v>
       </c>
       <c r="E8" s="262"/>
       <c r="F8" s="261"/>
@@ -42513,8 +42539,8 @@
     <row r="9" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="247"/>
       <c r="C9" s="246"/>
-      <c r="D9" s="290">
-        <v>57</v>
+      <c r="D9" s="290" t="s">
+        <v>375</v>
       </c>
       <c r="E9" s="289" t="s">
         <v>374</v>
@@ -42594,9 +42620,7 @@
     <row r="10" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="247"/>
       <c r="C10" s="246"/>
-      <c r="D10" s="308">
-        <v>70</v>
-      </c>
+      <c r="D10" s="308"/>
       <c r="E10" s="252"/>
       <c r="F10" s="251"/>
       <c r="G10" s="250" t="s">
@@ -42669,8 +42693,8 @@
     <row r="11" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="247"/>
       <c r="C11" s="246"/>
-      <c r="D11" s="250">
-        <v>53</v>
+      <c r="D11" s="250" t="s">
+        <v>4</v>
       </c>
       <c r="E11" s="249" t="s">
         <v>4</v>
@@ -42772,34 +42796,56 @@
     <row r="12" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="247"/>
       <c r="C12" s="246"/>
-      <c r="D12" s="304">
-        <v>59</v>
-      </c>
-      <c r="E12" s="303"/>
+      <c r="D12" s="304" t="s">
+        <v>344</v>
+      </c>
+      <c r="E12" s="303">
+        <v>24</v>
+      </c>
       <c r="F12" s="302"/>
-      <c r="G12" s="272"/>
-      <c r="H12" s="271"/>
-      <c r="I12" s="271"/>
-      <c r="J12" s="301"/>
-      <c r="K12" s="271"/>
-      <c r="L12" s="271"/>
-      <c r="M12" s="300"/>
-      <c r="N12" s="299"/>
-      <c r="O12" s="296"/>
+      <c r="G12" s="272">
+        <v>0</v>
+      </c>
+      <c r="H12" s="271">
+        <v>6</v>
+      </c>
+      <c r="I12" s="271">
+        <v>0</v>
+      </c>
+      <c r="J12" s="301">
+        <v>0</v>
+      </c>
+      <c r="K12" s="271">
+        <v>25</v>
+      </c>
+      <c r="L12" s="271">
+        <v>24</v>
+      </c>
+      <c r="M12" s="300">
+        <v>26</v>
+      </c>
+      <c r="N12" s="299">
+        <v>28</v>
+      </c>
+      <c r="O12" s="296">
+        <v>27</v>
+      </c>
       <c r="P12" s="298">
         <v>29.1</v>
       </c>
       <c r="Q12" s="274" t="s">
         <v>343</v>
       </c>
-      <c r="R12" s="271"/>
+      <c r="R12" s="271">
+        <v>11</v>
+      </c>
       <c r="S12" s="271">
         <f>R12-33.1</f>
         <v>-33.1</v>
       </c>
       <c r="T12" s="276"/>
-      <c r="U12" s="297" t="s">
-        <v>342</v>
+      <c r="U12" s="297">
+        <v>18</v>
       </c>
       <c r="V12" s="294">
         <v>1.6</v>
@@ -42807,7 +42853,9 @@
       <c r="W12" s="274">
         <v>17.600000000000001</v>
       </c>
-      <c r="X12" s="271"/>
+      <c r="X12" s="271">
+        <v>13</v>
+      </c>
       <c r="Y12" s="271">
         <f>X12-W12</f>
         <v>-17.600000000000001</v>
@@ -42816,24 +42864,38 @@
       <c r="AA12" s="274">
         <v>6.28</v>
       </c>
-      <c r="AB12" s="271"/>
+      <c r="AB12" s="271">
+        <v>0</v>
+      </c>
       <c r="AC12" s="271">
         <f>AB12-AA12</f>
         <v>-6.28</v>
       </c>
       <c r="AD12" s="296"/>
-      <c r="AE12" s="295"/>
-      <c r="AF12" s="294"/>
-      <c r="AG12" s="275"/>
-      <c r="AH12" s="276"/>
-      <c r="AI12" s="275"/>
-      <c r="AJ12" s="293"/>
+      <c r="AE12" s="295">
+        <v>40</v>
+      </c>
+      <c r="AF12" s="294">
+        <v>39</v>
+      </c>
+      <c r="AG12" s="275">
+        <v>53</v>
+      </c>
+      <c r="AH12" s="276">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="275">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="293">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="247"/>
       <c r="C13" s="246"/>
-      <c r="D13" s="292">
-        <v>67</v>
+      <c r="D13" s="292" t="s">
+        <v>341</v>
       </c>
       <c r="E13" s="261"/>
       <c r="F13" s="292" t="s">
@@ -42877,8 +42939,8 @@
     <row r="14" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="247"/>
       <c r="C14" s="246"/>
-      <c r="D14" s="290">
-        <v>55</v>
+      <c r="D14" s="290" t="s">
+        <v>337</v>
       </c>
       <c r="E14" s="251"/>
       <c r="F14" s="290" t="s">
@@ -42928,8 +42990,8 @@
     <row r="15" spans="2:36" s="227" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="247"/>
       <c r="C15" s="246"/>
-      <c r="D15" s="250">
-        <v>61</v>
+      <c r="D15" s="250" t="s">
+        <v>330</v>
       </c>
       <c r="E15" s="286" t="s">
         <v>327</v>
@@ -43031,8 +43093,8 @@
     <row r="16" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="247"/>
       <c r="C16" s="246"/>
-      <c r="D16" s="284">
-        <v>0</v>
+      <c r="D16" s="284" t="s">
+        <v>308</v>
       </c>
       <c r="E16" s="242" t="s">
         <v>4</v>
@@ -43135,68 +43197,96 @@
       <c r="B17" s="247"/>
       <c r="C17" s="246"/>
       <c r="D17" s="279">
-        <v>0</v>
-      </c>
-      <c r="E17" s="278"/>
-      <c r="F17" s="277" t="s">
-        <v>301</v>
+        <v>4</v>
+      </c>
+      <c r="E17" s="278">
+        <v>5</v>
+      </c>
+      <c r="F17" s="277">
+        <v>70</v>
       </c>
       <c r="G17" s="276">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="H17" s="275">
         <f>G17-F17</f>
         <v>4</v>
       </c>
-      <c r="I17" s="274"/>
-      <c r="J17" s="271"/>
+      <c r="I17" s="274">
+        <v>67</v>
+      </c>
+      <c r="J17" s="271">
+        <v>65</v>
+      </c>
       <c r="K17" s="271">
-        <v>93.5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="271">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="M17" s="273">
         <f>K17+L17</f>
-        <v>97.74</v>
+        <v>0</v>
       </c>
       <c r="N17" s="272">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O17" s="271">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="P17" s="270">
         <f>O17-N17</f>
         <v>3</v>
       </c>
-      <c r="Q17" s="267"/>
+      <c r="Q17" s="267">
+        <v>121</v>
+      </c>
       <c r="R17" s="267"/>
-      <c r="S17" s="267" t="s">
-        <v>300</v>
-      </c>
-      <c r="T17" s="267" t="s">
-        <v>299</v>
+      <c r="S17" s="267">
+        <v>0</v>
+      </c>
+      <c r="T17" s="267">
+        <v>0</v>
       </c>
       <c r="U17" s="269">
         <f>S17+T17</f>
-        <v>97.45</v>
-      </c>
-      <c r="V17" s="268"/>
-      <c r="W17" s="267"/>
-      <c r="X17" s="267"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="268">
+        <v>110</v>
+      </c>
+      <c r="W17" s="267">
+        <v>108</v>
+      </c>
+      <c r="X17" s="267">
+        <v>92</v>
+      </c>
       <c r="Y17" s="267"/>
-      <c r="Z17" s="267"/>
-      <c r="AA17" s="267"/>
-      <c r="AB17" s="267"/>
-      <c r="AC17" s="267"/>
-      <c r="AD17" s="267"/>
+      <c r="Z17" s="267">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="267">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="267">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="267">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="267">
+        <v>114</v>
+      </c>
       <c r="AE17" s="266" t="e">
         <f>Z17/AB17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF17" s="267"/>
-      <c r="AG17" s="267"/>
+      <c r="AF17" s="267">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="267">
+        <v>112</v>
+      </c>
       <c r="AH17" s="266" t="e">
         <f>AF17/(Z17-AB17)</f>
         <v>#DIV/0!</v>
@@ -43209,8 +43299,8 @@
     <row r="18" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="247"/>
       <c r="C18" s="246"/>
-      <c r="D18" s="263">
-        <v>64</v>
+      <c r="D18" s="263" t="s">
+        <v>297</v>
       </c>
       <c r="E18" s="262"/>
       <c r="F18" s="262"/>
@@ -43286,8 +43376,8 @@
     <row r="19" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="247"/>
       <c r="C19" s="246"/>
-      <c r="D19" s="256">
-        <v>122</v>
+      <c r="D19" s="256" t="s">
+        <v>296</v>
       </c>
       <c r="E19" s="252"/>
       <c r="F19" s="252"/>
@@ -43377,8 +43467,8 @@
     <row r="20" spans="2:36" s="227" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="247"/>
       <c r="C20" s="246"/>
-      <c r="D20" s="253">
-        <v>62</v>
+      <c r="D20" s="253" t="s">
+        <v>289</v>
       </c>
       <c r="E20" s="248" t="s">
         <v>288</v>
@@ -43470,8 +43560,8 @@
     <row r="21" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="247"/>
       <c r="C21" s="246"/>
-      <c r="D21" s="245">
-        <v>121</v>
+      <c r="D21" s="245" t="s">
+        <v>286</v>
       </c>
       <c r="E21" s="244" t="s">
         <v>286</v>
@@ -43574,32 +43664,48 @@
       <c r="B22" s="247"/>
       <c r="C22" s="246"/>
       <c r="D22" s="355">
-        <v>11</v>
-      </c>
-      <c r="E22" s="354"/>
+        <v>51</v>
+      </c>
+      <c r="E22" s="354">
+        <v>57</v>
+      </c>
       <c r="F22" s="354">
         <f>D22-E22</f>
         <v>0</v>
       </c>
-      <c r="G22" s="354"/>
-      <c r="H22" s="354"/>
+      <c r="G22" s="354">
+        <v>53</v>
+      </c>
+      <c r="H22" s="354">
+        <v>59</v>
+      </c>
       <c r="I22" s="354">
         <f>G22-H22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="354"/>
-      <c r="K22" s="354"/>
+      <c r="J22" s="354">
+        <v>55</v>
+      </c>
+      <c r="K22" s="354">
+        <v>61</v>
+      </c>
       <c r="L22" s="354">
         <f>J22-K22</f>
         <v>0</v>
       </c>
-      <c r="M22" s="354"/>
-      <c r="N22" s="354"/>
+      <c r="M22" s="354">
+        <v>0</v>
+      </c>
+      <c r="N22" s="354">
+        <v>64</v>
+      </c>
       <c r="O22" s="357" t="e">
         <f>N22/M22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P22" s="354"/>
+      <c r="P22" s="354">
+        <v>62</v>
+      </c>
       <c r="Q22" s="356">
         <v>301</v>
       </c>
@@ -43664,9 +43770,7 @@
     <row r="23" spans="2:36" s="227" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="350"/>
       <c r="C23" s="349"/>
-      <c r="D23" s="348">
-        <v>0</v>
-      </c>
+      <c r="D23" s="348"/>
       <c r="E23" s="348"/>
       <c r="F23" s="348"/>
       <c r="G23" s="348"/>
@@ -43707,8 +43811,8 @@
       <c r="C24" s="343" t="s">
         <v>413</v>
       </c>
-      <c r="D24" s="342">
-        <v>0</v>
+      <c r="D24" s="342" t="s">
+        <v>412</v>
       </c>
       <c r="E24" s="341"/>
       <c r="F24" s="341"/>
@@ -43748,8 +43852,8 @@
     <row r="25" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="247"/>
       <c r="C25" s="246"/>
-      <c r="D25" s="337">
-        <v>0</v>
+      <c r="D25" s="337" t="s">
+        <v>410</v>
       </c>
       <c r="E25" s="163"/>
       <c r="F25" s="163"/>
@@ -43811,8 +43915,8 @@
     <row r="26" spans="2:36" s="227" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="331"/>
       <c r="C26" s="330"/>
-      <c r="D26" s="253">
-        <v>110</v>
+      <c r="D26" s="253" t="s">
+        <v>398</v>
       </c>
       <c r="E26" s="248" t="s">
         <v>397</v>
@@ -43898,8 +44002,8 @@
       <c r="C27" s="324" t="s">
         <v>382</v>
       </c>
-      <c r="D27" s="241">
-        <v>108</v>
+      <c r="D27" s="241" t="s">
+        <v>283</v>
       </c>
       <c r="E27" s="240" t="s">
         <v>283</v>
@@ -44003,35 +44107,61 @@
       <c r="C28" s="246"/>
       <c r="D28" s="272">
         <f>J28+U28</f>
-        <v>92</v>
+        <v>310</v>
       </c>
       <c r="E28" s="271">
         <f>K28+V28</f>
-        <v>0</v>
+        <v>83.09999084472656</v>
       </c>
       <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="321"/>
-      <c r="J28" s="320"/>
-      <c r="K28" s="319"/>
-      <c r="L28" s="319"/>
+      <c r="G28" s="271">
+        <v>0</v>
+      </c>
+      <c r="H28" s="271">
+        <v>0</v>
+      </c>
+      <c r="I28" s="321">
+        <v>0</v>
+      </c>
+      <c r="J28" s="320">
+        <v>0</v>
+      </c>
+      <c r="K28" s="319">
+        <v>0</v>
+      </c>
+      <c r="L28" s="319">
+        <v>0</v>
+      </c>
       <c r="M28" s="319"/>
       <c r="N28" s="319"/>
-      <c r="O28" s="319"/>
+      <c r="O28" s="319">
+        <v>0</v>
+      </c>
       <c r="P28" s="319"/>
       <c r="Q28" s="319"/>
-      <c r="R28" s="319"/>
+      <c r="R28" s="319">
+        <v>0</v>
+      </c>
       <c r="S28" s="318"/>
       <c r="T28" s="317"/>
-      <c r="U28" s="316"/>
-      <c r="V28" s="315"/>
-      <c r="W28" s="267"/>
-      <c r="X28" s="271"/>
-      <c r="Y28" s="271"/>
-      <c r="Z28" s="314" t="e">
+      <c r="U28" s="316">
+        <v>0</v>
+      </c>
+      <c r="V28" s="315">
+        <v>0</v>
+      </c>
+      <c r="W28" s="267">
+        <v>0</v>
+      </c>
+      <c r="X28" s="271">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="271">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="314">
         <f>U28/D28</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="313"/>
       <c r="AB28" s="300"/>
@@ -44047,8 +44177,8 @@
     <row r="29" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="247"/>
       <c r="C29" s="246"/>
-      <c r="D29" s="292">
-        <v>0</v>
+      <c r="D29" s="292" t="s">
+        <v>378</v>
       </c>
       <c r="E29" s="262"/>
       <c r="F29" s="261"/>
@@ -44092,8 +44222,8 @@
     <row r="30" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="247"/>
       <c r="C30" s="246"/>
-      <c r="D30" s="290">
-        <v>0</v>
+      <c r="D30" s="290" t="s">
+        <v>375</v>
       </c>
       <c r="E30" s="289" t="s">
         <v>374</v>
@@ -44173,9 +44303,7 @@
     <row r="31" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="247"/>
       <c r="C31" s="246"/>
-      <c r="D31" s="308">
-        <v>51</v>
-      </c>
+      <c r="D31" s="308"/>
       <c r="E31" s="252"/>
       <c r="F31" s="251"/>
       <c r="G31" s="250" t="s">
@@ -44248,8 +44376,8 @@
     <row r="32" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="247"/>
       <c r="C32" s="246"/>
-      <c r="D32" s="250">
-        <v>57</v>
+      <c r="D32" s="250" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="249" t="s">
         <v>4</v>
@@ -44351,34 +44479,56 @@
     <row r="33" spans="2:36" s="227" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="247"/>
       <c r="C33" s="246"/>
-      <c r="D33" s="304">
-        <v>70</v>
-      </c>
-      <c r="E33" s="303"/>
+      <c r="D33" s="304" t="s">
+        <v>344</v>
+      </c>
+      <c r="E33" s="303">
+        <v>24</v>
+      </c>
       <c r="F33" s="302"/>
-      <c r="G33" s="272"/>
-      <c r="H33" s="271"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="301"/>
-      <c r="K33" s="271"/>
-      <c r="L33" s="271"/>
-      <c r="M33" s="300"/>
-      <c r="N33" s="299"/>
-      <c r="O33" s="296"/>
+      <c r="G33" s="272">
+        <v>0</v>
+      </c>
+      <c r="H33" s="271">
+        <v>6</v>
+      </c>
+      <c r="I33" s="271">
+        <v>0</v>
+      </c>
+      <c r="J33" s="301">
+        <v>0</v>
+      </c>
+      <c r="K33" s="271">
+        <v>25</v>
+      </c>
+      <c r="L33" s="271">
+        <v>24</v>
+      </c>
+      <c r="M33" s="300">
+        <v>26</v>
+      </c>
+      <c r="N33" s="299">
+        <v>28</v>
+      </c>
+      <c r="O33" s="296">
+        <v>27</v>
+      </c>
       <c r="P33" s="298">
         <v>29.1</v>
       </c>
       <c r="Q33" s="274" t="s">
         <v>343</v>
       </c>
-      <c r="R33" s="271"/>
+      <c r="R33" s="271">
+        <v>11</v>
+      </c>
       <c r="S33" s="271">
         <f>R33-33.1</f>
         <v>-33.1</v>
       </c>
       <c r="T33" s="276"/>
-      <c r="U33" s="297" t="s">
-        <v>342</v>
+      <c r="U33" s="297">
+        <v>18</v>
       </c>
       <c r="V33" s="294">
         <v>1.6</v>
@@ -44386,7 +44536,9 @@
       <c r="W33" s="274">
         <v>17.600000000000001</v>
       </c>
-      <c r="X33" s="271"/>
+      <c r="X33" s="271">
+        <v>13</v>
+      </c>
       <c r="Y33" s="271">
         <f>X33-W33</f>
         <v>-17.600000000000001</v>
@@ -44395,24 +44547,38 @@
       <c r="AA33" s="274">
         <v>6.28</v>
       </c>
-      <c r="AB33" s="271"/>
+      <c r="AB33" s="271">
+        <v>0</v>
+      </c>
       <c r="AC33" s="271">
         <f>AB33-AA33</f>
         <v>-6.28</v>
       </c>
       <c r="AD33" s="296"/>
-      <c r="AE33" s="295"/>
-      <c r="AF33" s="294"/>
-      <c r="AG33" s="275"/>
-      <c r="AH33" s="276"/>
-      <c r="AI33" s="275"/>
-      <c r="AJ33" s="293"/>
+      <c r="AE33" s="295">
+        <v>40</v>
+      </c>
+      <c r="AF33" s="294">
+        <v>39</v>
+      </c>
+      <c r="AG33" s="275">
+        <v>53</v>
+      </c>
+      <c r="AH33" s="276">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="275">
+        <v>2</v>
+      </c>
+      <c r="AJ33" s="293">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="247"/>
       <c r="C34" s="246"/>
-      <c r="D34" s="292">
-        <v>53</v>
+      <c r="D34" s="292" t="s">
+        <v>341</v>
       </c>
       <c r="E34" s="261"/>
       <c r="F34" s="292" t="s">
@@ -44456,8 +44622,8 @@
     <row r="35" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="247"/>
       <c r="C35" s="246"/>
-      <c r="D35" s="290">
-        <v>59</v>
+      <c r="D35" s="290" t="s">
+        <v>337</v>
       </c>
       <c r="E35" s="251"/>
       <c r="F35" s="290" t="s">
@@ -44507,8 +44673,8 @@
     <row r="36" spans="2:36" s="227" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="247"/>
       <c r="C36" s="246"/>
-      <c r="D36" s="250">
-        <v>67</v>
+      <c r="D36" s="250" t="s">
+        <v>330</v>
       </c>
       <c r="E36" s="286" t="s">
         <v>327</v>
@@ -44610,8 +44776,8 @@
     <row r="37" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="247"/>
       <c r="C37" s="246"/>
-      <c r="D37" s="284">
-        <v>55</v>
+      <c r="D37" s="284" t="s">
+        <v>308</v>
       </c>
       <c r="E37" s="242" t="s">
         <v>4</v>
@@ -44714,68 +44880,96 @@
       <c r="B38" s="247"/>
       <c r="C38" s="246"/>
       <c r="D38" s="279">
-        <v>61</v>
-      </c>
-      <c r="E38" s="278"/>
-      <c r="F38" s="277" t="s">
-        <v>301</v>
+        <v>4</v>
+      </c>
+      <c r="E38" s="278">
+        <v>5</v>
+      </c>
+      <c r="F38" s="277">
+        <v>70</v>
       </c>
       <c r="G38" s="276">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="H38" s="275">
         <f>G38-F38</f>
         <v>4</v>
       </c>
-      <c r="I38" s="274"/>
-      <c r="J38" s="271"/>
+      <c r="I38" s="274">
+        <v>67</v>
+      </c>
+      <c r="J38" s="271">
+        <v>65</v>
+      </c>
       <c r="K38" s="271">
-        <v>93.5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="271">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="M38" s="273">
         <f>K38+L38</f>
-        <v>97.74</v>
+        <v>0</v>
       </c>
       <c r="N38" s="272">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O38" s="271">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="P38" s="270">
         <f>O38-N38</f>
         <v>3</v>
       </c>
-      <c r="Q38" s="267"/>
+      <c r="Q38" s="267">
+        <v>121</v>
+      </c>
       <c r="R38" s="267"/>
-      <c r="S38" s="267" t="s">
-        <v>300</v>
-      </c>
-      <c r="T38" s="267" t="s">
-        <v>299</v>
+      <c r="S38" s="267">
+        <v>0</v>
+      </c>
+      <c r="T38" s="267">
+        <v>0</v>
       </c>
       <c r="U38" s="269">
         <f>S38+T38</f>
-        <v>97.45</v>
-      </c>
-      <c r="V38" s="268"/>
-      <c r="W38" s="267"/>
-      <c r="X38" s="267"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="268">
+        <v>110</v>
+      </c>
+      <c r="W38" s="267">
+        <v>108</v>
+      </c>
+      <c r="X38" s="267">
+        <v>92</v>
+      </c>
       <c r="Y38" s="267"/>
-      <c r="Z38" s="267"/>
-      <c r="AA38" s="267"/>
-      <c r="AB38" s="267"/>
-      <c r="AC38" s="267"/>
-      <c r="AD38" s="267"/>
+      <c r="Z38" s="267">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="267">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="267">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="267">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="267">
+        <v>114</v>
+      </c>
       <c r="AE38" s="266" t="e">
         <f>Z38/AB38</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF38" s="267"/>
-      <c r="AG38" s="267"/>
+      <c r="AF38" s="267">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="267">
+        <v>112</v>
+      </c>
       <c r="AH38" s="266" t="e">
         <f>AF38/(Z38-AB38)</f>
         <v>#DIV/0!</v>
@@ -44788,8 +44982,8 @@
     <row r="39" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="247"/>
       <c r="C39" s="246"/>
-      <c r="D39" s="263">
-        <v>0</v>
+      <c r="D39" s="263" t="s">
+        <v>297</v>
       </c>
       <c r="E39" s="262"/>
       <c r="F39" s="262"/>
@@ -44865,8 +45059,8 @@
     <row r="40" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="247"/>
       <c r="C40" s="246"/>
-      <c r="D40" s="256">
-        <v>0</v>
+      <c r="D40" s="256" t="s">
+        <v>296</v>
       </c>
       <c r="E40" s="252"/>
       <c r="F40" s="252"/>
@@ -44956,8 +45150,8 @@
     <row r="41" spans="2:36" s="227" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="247"/>
       <c r="C41" s="246"/>
-      <c r="D41" s="253">
-        <v>64</v>
+      <c r="D41" s="253" t="s">
+        <v>289</v>
       </c>
       <c r="E41" s="248" t="s">
         <v>288</v>
@@ -45049,8 +45243,8 @@
     <row r="42" spans="2:36" s="227" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B42" s="247"/>
       <c r="C42" s="246"/>
-      <c r="D42" s="245">
-        <v>122</v>
+      <c r="D42" s="245" t="s">
+        <v>286</v>
       </c>
       <c r="E42" s="244" t="s">
         <v>286</v>
@@ -45153,32 +45347,48 @@
       <c r="B43" s="236"/>
       <c r="C43" s="235"/>
       <c r="D43" s="232">
-        <v>62</v>
-      </c>
-      <c r="E43" s="231"/>
+        <v>51</v>
+      </c>
+      <c r="E43" s="231">
+        <v>57</v>
+      </c>
       <c r="F43" s="231">
         <f>D43-E43</f>
         <v>0</v>
       </c>
-      <c r="G43" s="231"/>
-      <c r="H43" s="231"/>
+      <c r="G43" s="231">
+        <v>53</v>
+      </c>
+      <c r="H43" s="231">
+        <v>59</v>
+      </c>
       <c r="I43" s="231">
         <f>G43-H43</f>
         <v>0</v>
       </c>
-      <c r="J43" s="231"/>
-      <c r="K43" s="231"/>
+      <c r="J43" s="231">
+        <v>55</v>
+      </c>
+      <c r="K43" s="231">
+        <v>61</v>
+      </c>
       <c r="L43" s="231">
         <f>J43-K43</f>
         <v>0</v>
       </c>
-      <c r="M43" s="231"/>
-      <c r="N43" s="231"/>
+      <c r="M43" s="231">
+        <v>0</v>
+      </c>
+      <c r="N43" s="231">
+        <v>64</v>
+      </c>
       <c r="O43" s="234" t="e">
         <f>N43/M43</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P43" s="231"/>
+      <c r="P43" s="231">
+        <v>62</v>
+      </c>
       <c r="Q43" s="233">
         <v>301</v>
       </c>
@@ -45240,106 +45450,26 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D44" s="0">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D45" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D46" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D47" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D48" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D49" s="0">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D50" s="0">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D51" s="0">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D52" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D53" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D54" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D55" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D56" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D57" s="0">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D58" s="0">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D59" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D60" s="0">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D61" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D62" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="D63" s="0">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="44" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="2:36" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="64" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="65" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="66" ht="18" customHeight="1" x14ac:dyDescent="0.4"/>
